--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3555-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3555-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F08F293A-C1C5-4552-846F-A98021B1790D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB2DFE29-600B-40BC-BB82-E1E798EA82EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{C2513B10-B9F6-443E-9CE2-9C76B0E6D1AF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{0B849FF2-2A85-42E7-A64C-7AB52B01AE4D}"/>
   </bookViews>
   <sheets>
     <sheet name="3555-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1454,25 +1454,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DE0E94-73F4-46A5-8197-0BF6EA75198E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73BC3DE-67A8-4E7C-BF6F-76A4BDC596B8}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1626,7 +1626,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2023</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2021</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2020</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2019</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2018</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2017</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2016</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2015</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2014</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2013</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2012</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2011</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2010</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2009</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2008</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2007</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
         <v>37</v>
       </c>
